--- a/source-data/Enerium_Лавка.xlsx
+++ b/source-data/Enerium_Лавка.xlsx
@@ -181,7 +181,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">acc859dc76a60f5e — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">9014ebd7919d1c0e — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">рунные ключи 5, души 200, Энериум 150</t>
+          <t xml:space="preserve">рунные ключи 5, души 150, Энериум 150</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">рунные ключи 10, души 400, Энериум 500</t>
+          <t xml:space="preserve">рунные ключи 10, души 300, Энериум 500</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">рунные ключи 15, души 600, Энериум 1000</t>
+          <t xml:space="preserve">рунные ключи 15, души 450, Энериум 1000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">рунные ключи 20, души 800, Энериум 2000</t>
+          <t xml:space="preserve">рунные ключи 20, души 650, Энериум 2000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">рунные ключи 30, души 1500, Энериум 5000</t>
+          <t xml:space="preserve">рунные ключи 30, души 1300, Энериум 5000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">

--- a/source-data/Enerium_Лавка.xlsx
+++ b/source-data/Enerium_Лавка.xlsx
@@ -181,7 +181,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9014ebd7919d1c0e — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">23b618f1224f4feb — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">рунные ключи 20, души 650, Энериум 2000</t>
+          <t xml:space="preserve">рунные ключи 20, души 600, Энериум 2000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">рунные ключи 30, души 1300, Энериум 5000</t>
+          <t xml:space="preserve">рунные ключи 30, души 1200, Энериум 5000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">

--- a/source-data/Enerium_Лавка.xlsx
+++ b/source-data/Enerium_Лавка.xlsx
@@ -7,7 +7,7 @@
   <sheets>
     <sheet name="Как читать" sheetId="1" r:id="rId1"/>
     <sheet name="Цены" sheetId="2" r:id="rId2"/>
-    <sheet name="Стартовые наборы" sheetId="3" r:id="rId3"/>
+    <sheet name="Разовые наборы" sheetId="3" r:id="rId3"/>
     <sheet name="Наборы Энериума" sheetId="4" r:id="rId4"/>
     <sheet name="Выдачи" sheetId="5" r:id="rId5"/>
     <sheet name="Предложения" sheetId="6" r:id="rId6"/>
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Цены'!$A$1:$C$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Стартовые наборы'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Разовые наборы'!$A$1:$F$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Наборы Энериума'!$A$1:$F$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Выдачи'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Предложения'!$A$1:$F$4</definedName>
@@ -144,7 +144,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Витрина доната (§32, ADR-0036): ступени цен для России и Запада, пять стартовых наборов цепочкой (все ×2), пять наборов Энериума (первая покупка ×2), три выдачи раз в сутки, платный ряд пропуска, лимитированные предложения, реклама за Энериум по желанию.</t>
+          <t xml:space="preserve">Витрина доната (§32, ADR-0036, ADR-0047, ADR-0054): курс — 1 ₽ = 1 Энериум; ступени цен для России и Запада; пять разовых наборов — каждый раз за игру, в любом порядке, ×2 получает только самая первая покупка, набор выбирает игрок; пять наборов Энериума — ×2 первой покупке каждого набора; три выдачи раз в сутки, платный ряд пропуска, лимитированные предложения, реклама за Энериум по желанию.</t>
         </is>
       </c>
     </row>
@@ -169,7 +169,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-07 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -181,7 +181,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">23b618f1224f4feb — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">d8cdca5b69541d31 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лист «Стартовые наборы»</t>
+          <t xml:space="preserve">Лист «Разовые наборы»</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -320,8 +320,8 @@
 III — слабые, почти незаметные намёки — слово-отзвук без имени тайны (ADR-0022: намёки на Странника — с цикла III)
 IV — заметнее, но всё ещё намёки: иносказание, без прямых имён и формулировок тайны
 V — намёки очевиднее («начиная с 5 будут намёки»); прямого раскрытия §38 нет
-VI — только для команды: здесь тайны названы прямо
-Ступени слов: D — прямое раскрытие — только цикл VI, для команды; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
+VI — раскрытие: в текстах игрока цикла VI тайны могут быть названы прямо (ADR-0054); в текстах циклов I–V — нет
+Ступени слов: D — прямое раскрытие — только с цикла VI: игрок получает его в игре, раньше — нет; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
 Проверка — node tools/content-gen/tables/check_spoilers.js; все совпадения по циклам — «Реестр имён», лист «Намёки по циклам».</t>
         </is>
       </c>
@@ -534,13 +534,13 @@
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Шаг</t>
+          <t xml:space="preserve">№</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Множитель</t>
+          <t xml:space="preserve">Удвоение</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">рунные ключи 5, души 150, Энериум 150</t>
+          <t xml:space="preserve">рунные ключи 5, души 150, Энериум 100</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">×2</t>
+          <t xml:space="preserve">×2 — если куплен первым</t>
         </is>
       </c>
     </row>
@@ -620,12 +620,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">рунные ключи 10, души 300, Энериум 500</t>
+          <t xml:space="preserve">рунные ключи 10, души 300, Энериум 250</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">×2</t>
+          <t xml:space="preserve">×2 — если куплен первым</t>
         </is>
       </c>
     </row>
@@ -650,12 +650,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">рунные ключи 15, души 450, Энериум 1000</t>
+          <t xml:space="preserve">рунные ключи 15, души 450, Энериум 500</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">×2</t>
+          <t xml:space="preserve">×2 — если куплен первым</t>
         </is>
       </c>
     </row>
@@ -680,12 +680,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">рунные ключи 20, души 600, Энериум 2000</t>
+          <t xml:space="preserve">рунные ключи 20, души 600, Энериум 1000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">×2</t>
+          <t xml:space="preserve">×2 — если куплен первым</t>
         </is>
       </c>
     </row>
@@ -710,12 +710,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">рунные ключи 30, души 1200, Энериум 5000</t>
+          <t xml:space="preserve">рунные ключи 30, души 1200, Энериум 2500</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">×2</t>
+          <t xml:space="preserve">×2 — если куплен первым</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E3">
         <v>1000</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E4">
         <v>2000</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="E5">
         <v>3000</v>
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="E6">
         <v>4000</v>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>30</v>
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="E3">
         <v>30</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E4">
         <v>30</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Энериум 1000</t>
+          <t xml:space="preserve">Энериум 500</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Энериум 2000</t>
+          <t xml:space="preserve">Энериум 1000</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Энериум 2000</t>
+          <t xml:space="preserve">Энериум 1000</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Энериум 4000</t>
+          <t xml:space="preserve">Энериум 2000</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Энериум 4000</t>
+          <t xml:space="preserve">Энериум 2000</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Энериум 1500</t>
+          <t xml:space="preserve">Энериум 750</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Энериум 3000</t>
+          <t xml:space="preserve">Энериум 1500</t>
         </is>
       </c>
     </row>
